--- a/Analysis/02_CGE_EIPI/3_eipi_selection_diagnostics.xlsx
+++ b/Analysis/02_CGE_EIPI/3_eipi_selection_diagnostics.xlsx
@@ -478,7 +478,7 @@
         <v>0.923245448364433</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1258845156253935</v>
+        <v>-0.1302158092216263</v>
       </c>
       <c r="H2" t="n">
         <v>0.0749666339301453</v>
@@ -506,7 +506,7 @@
         <v>0.8238775150462089</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1086600689985143</v>
+        <v>-0.1920626526655083</v>
       </c>
       <c r="H3" t="n">
         <v>-0.1839037042633024</v>
@@ -534,7 +534,7 @@
         <v>-0.1005011205963083</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7610737579008335</v>
+        <v>0.4976203067160233</v>
       </c>
       <c r="H4" t="n">
         <v>-0.1307194480118859</v>
@@ -562,7 +562,7 @@
         <v>-0.01820654226788547</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06172093374631714</v>
+        <v>0.1195890307471481</v>
       </c>
       <c r="H5" t="n">
         <v>-0.07607463926871648</v>
@@ -590,7 +590,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.03180478960489537</v>
+        <v>0.04958323890106016</v>
       </c>
       <c r="H6" t="n">
         <v>0.1771045805947974</v>
@@ -603,25 +603,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1258845156253935</v>
+        <v>-0.1302158092216263</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1086600689985143</v>
+        <v>-0.1920626526655083</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7610737579008335</v>
+        <v>0.4976203067160233</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06172093374631714</v>
+        <v>0.1195890307471481</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.03180478960489537</v>
+        <v>0.04958323890106016</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2078769106796605</v>
+        <v>0.3266853013019063</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>0.1771045805947974</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2078769106796605</v>
+        <v>0.3266853013019063</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.55571772242428</v>
+        <v>19.52914862351321</v>
       </c>
     </row>
     <row r="3">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.65628136009784</v>
+        <v>32.23428363546736</v>
       </c>
     </row>
     <row r="4">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.117715750407075</v>
+        <v>2.638283711557242</v>
       </c>
     </row>
     <row r="5">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.179215840312358</v>
+        <v>2.24290978303489</v>
       </c>
     </row>
     <row r="6">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.9929787423301</v>
+        <v>17.39394284720505</v>
       </c>
     </row>
     <row r="7">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.654298099750599</v>
+        <v>5.55449544121741</v>
       </c>
     </row>
     <row r="8">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.712267994979408</v>
+        <v>7.21948875492359</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5036922267790511</v>
+        <v>0.4743140718450339</v>
       </c>
     </row>
     <row r="5">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>445.0998408197434</v>
+        <v>426.5550189661681</v>
       </c>
     </row>
     <row r="6">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.100886794165617e-81</v>
+        <v>2.918007857971452e-77</v>
       </c>
     </row>
   </sheetData>
